--- a/Result/profitability/2107.xlsx
+++ b/Result/profitability/2107.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.54</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4</v>
+        <v>0.4325</v>
       </c>
       <c r="N2" t="n">
-        <v>34.5175</v>
+        <v>35.85625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.26</v>
       </c>
       <c r="M3" t="n">
-        <v>0.35125</v>
+        <v>0.4525</v>
       </c>
       <c r="N3" t="n">
-        <v>35.315</v>
+        <v>36.44125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.54</v>
       </c>
       <c r="M4" t="n">
-        <v>0.40625</v>
+        <v>0.46125</v>
       </c>
       <c r="N4" t="n">
-        <v>36.38125</v>
+        <v>36.23375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.42</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4</v>
+        <v>0.45625</v>
       </c>
       <c r="N5" t="n">
-        <v>36.87625</v>
+        <v>38.43625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.55</v>
       </c>
       <c r="M6" t="n">
-        <v>0.41125</v>
+        <v>0.45125</v>
       </c>
       <c r="N6" t="n">
-        <v>39.2</v>
+        <v>40.945</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,13 +1264,13 @@
         <v>0.43</v>
       </c>
       <c r="M7" t="n">
-        <v>0.39125</v>
+        <v>0.485</v>
       </c>
       <c r="N7" t="n">
-        <v>41.04375</v>
+        <v>42.75125</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.64</v>
       </c>
       <c r="M8" t="n">
-        <v>0.45125</v>
+        <v>0.53625</v>
       </c>
       <c r="N8" t="n">
-        <v>43.58125</v>
+        <v>44.8725</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1412,7 +1412,7 @@
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
         <v>1</v>
@@ -1518,10 +1518,10 @@
         <v>0.6</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4975000000000001</v>
+        <v>0.4975</v>
       </c>
       <c r="N9" t="n">
-        <v>44.59375</v>
+        <v>44.59374999999999</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>0.70625</v>
       </c>
       <c r="N13" t="n">
-        <v>47.225</v>
+        <v>47.22499999999999</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2107</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>421</v>
+      </c>
+      <c r="D75" t="n">
+        <v>237</v>
+      </c>
+      <c r="E75" t="n">
+        <v>183</v>
+      </c>
+      <c r="F75" t="n">
+        <v>43.59</v>
+      </c>
+      <c r="G75" t="n">
+        <v>135</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>32.13%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>180</v>
+      </c>
+      <c r="J75" t="n">
+        <v>315</v>
+      </c>
+      <c r="K75" t="n">
+        <v>276</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.44625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>34.96875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2.956521739130435</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>10.33000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.310583283223091</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.9782608695652173</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.4011571841851496</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
